--- a/artfynd/A 45865-2024 artfynd.xlsx
+++ b/artfynd/A 45865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150664</v>
       </c>
       <c r="B2" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45865-2024 artfynd.xlsx
+++ b/artfynd/A 45865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150664</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45865-2024 artfynd.xlsx
+++ b/artfynd/A 45865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150664</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
